--- a/content/Question Bank/MCQ/Unit 8 - Functions/Unit 8 - Functions - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Unit 8 - Functions/Unit 8 - Functions - MCQ.xlsx
@@ -1331,7 +1331,8 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>```python
+          <t>A payroll script needs 5! (factorial of 5) for a bonus calculation, so a developer writes a recursive function but forgets to give it a stopping condition.
+```python
 def broken_factorial(n):
     return n * broken_factorial(n - 1)
 broken_factorial(5)
@@ -1515,7 +1516,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>What problem does writing a function solve that copy-pasting the same logic everywhere does not?</t>
+          <t>A weather app has the same temperature-conversion formula pasted into five different screens, and now a bug fix has to be repeated in all five places. What problem does writing a function solve that copy-pasting the same logic everywhere does not?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1593,7 +1594,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Which line correctly starts a function definition named greet that takes no parameters?</t>
+          <t>A developer building a chat app wants to write a simple greet function that runs with no inputs at all, just to print a welcome banner when the app opens. Which line correctly starts a function definition named greet that takes no parameters?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1671,7 +1672,8 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>```python
+          <t>A club membership app defines a function that welcomes a new member by name, then immediately calls it for a member named Asha.
+```python
 def greet_member():
     print("Welcome!")
 print("Script finished.")
@@ -1754,7 +1756,8 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>```python
+          <t>A chat app defines a greet function that takes a username and prints a welcome message when a new user logs in.
+```python
 def greet(name):
     print(f"Welcome, {name}!")
 greet("Asha")
@@ -1837,7 +1840,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>What value does a function return if it has no return statement at all?</t>
+          <t>A food delivery app has a function that logs an order but never explicitly returns anything, and another part of the code tries to use whatever the function "gives back". What value does a function return if it has no return statement at all?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1915,7 +1918,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A developer copy-pastes the same bill-splitting calculation into three different scripts. The formula later needs a service charge added. What is the main risk of this approach?</t>
+          <t>A developer copy-pastes the same bill-splitting calculation into three different scripts for a trip-planning app. The formula later needs a service charge added. What is the main risk of this approach?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1993,7 +1996,8 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>```python
+          <t>A club onboarding script calls its greeting function before the function has actually been defined anywhere in the file.
+```python
 say_hello()
 def say_hello():
     print("Hello!")
@@ -2076,7 +2080,8 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>```python
+          <t>A calculator app adds two numbers inside a function and prints the sum, but the caller also tries to capture and reuse the function's return value.
+```python
 def add_no_return(a, b):
     print(a + b)
 result = add_no_return(3, 4)
@@ -2160,7 +2165,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A developer writes `calculate_total(price, quantity)` expecting to use its result in a later calculation, but forgets to include a return statement, only printing the value inside the function. What happens when the result is used afterward?</t>
+          <t>A billing system writes `calculate_total(price, quantity)` expecting to use its result in a later calculation, but forgets to include a return statement, only printing the value inside the function. What happens when the result is used afterward?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2238,7 +2243,8 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>```python
+          <t>A club treasurer wants a function that can accept any number of member contributions in one call and add them all up, without fixing the number of arguments in advance.
+```python
 def total_contributions(*amounts):
     return sum(amounts)
 print(total_contributions(500, 400, 600))
@@ -2422,7 +2428,8 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>```python
+          <t>A student registration form wants to accept any combination of optional profile fields, like name and year, without hardcoding each one as a separate parameter.
+```python
 def build_profile(**details):
     return details
 profile = build_profile(name="Naveen", year=2)
@@ -2506,7 +2513,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Which lambda correctly squares its input, equivalent to def `square(x)`: return x * x?</t>
+          <t>A math tutoring app needs a one-line helper to square any number a student enters, without writing a full function definition for something this small. Which lambda correctly squares its input, equivalent to def `square(x)`: return x * x?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2584,7 +2591,8 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>```python
+          <t>A trip-planning app's bill-splitting function accidentally places a default-valued parameter before a required one when it's defined.
+```python
 def split_cost(total, service_charge=0, people):
     return (total + service_charge) / people
 ```
@@ -2666,7 +2674,8 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>```python
+          <t>A trip-planning app calls its bill-splitting function while mixing a keyword argument with a positional one in the wrong order.
+```python
 print(split_cost(total=1200, 4))
 ```
 Why does this call fail?</t>
@@ -2747,7 +2756,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Which parameter order is valid in a function definition that uses ordinary parameters, *args, and **kwargs together?</t>
+          <t>A reporting tool needs a function that accepts a few fixed fields, then any number of extra positional values, then any number of extra named values, all in one signature. Which parameter order is valid in a function definition that uses ordinary parameters, *args, and **kwargs together?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2825,7 +2834,8 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A developer writes def `report(**details, *items)`: and expects it to work like ordinary parameters followed by *args then **kwargs. What actually happens?</t>
+          <t>A reporting tool's developer defines a function meant to accept ordinary fields plus flexible extras, but writes the **kwargs collector before the *args collector by mistake.
+A developer writes def `report(**details, *items)`: and expects it to work like ordinary parameters followed by *args then **kwargs. What actually happens?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2903,7 +2913,8 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>```python
+          <t>A club treasurer wants to apply a 5% late fee to every member's outstanding dues in one line, without writing a manual loop.
+```python
 dues = [300, 150, 450]
 result = list(map(lambda amount: amount * 1.05, dues))
 ```
@@ -2985,7 +2996,8 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>```python
+          <t>A finance app wants to flag only the transactions above Rs 200 out of a list of recent payment amounts, using a single filter call instead of a manual loop.
+```python
 values = [315.0, 157.5, 472.5, 210.0]
 result = list(filter(lambda amount: amount &gt; 200, values))
 ```
@@ -3067,7 +3079,8 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>```python
+          <t>A club treasurer tracks whether each member has paid their dues and wants a one-line check for whether everyone has paid.
+```python
 paid = [True, True, False]
 print(all(paid))
 ```
@@ -3149,7 +3162,8 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>```python
+          <t>A billing script defines a currency-formatting helper nested inside its receipt-printing function, then tries to call that helper directly from outside afterward.
+```python
 def print_receipt(item, price):
     def format_currency(amount):
         return f"Rs {amount:.2f}"
@@ -3336,7 +3350,8 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>```python
+          <t>A billing script computes an order's total inside a function and a later line outside the function tries to reuse that same total variable directly.
+```python
 def calculate_total(prices):
     total = sum(prices)
     return total
@@ -3421,7 +3436,8 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>```python
+          <t>An event registration function needs to accept the event name, any number of attendee names, and any number of extra named details like the venue, all in one call.
+```python
 def register(event, *attendees, **details):
     print(attendees)
     print(details)
@@ -3505,7 +3521,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Why can a lambda not contain a loop or an if statement spanning multiple lines, unlike a def function?</t>
+          <t>A form-validation script tries to squeeze a multi-branch eligibility check with a loop into a single lambda expression. Why can a lambda not contain a loop or an if statement spanning multiple lines, unlike a def function?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3583,7 +3599,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A developer uses from functools import reduce and `reduce(lambda a, b: a + b, numbers)` purely to add up a list of numbers. What would experienced Python programmers point out?</t>
+          <t>A finance app developer uses from functools import reduce and `reduce(lambda a, b: a + b, numbers)` purely to add up a list of monthly expenses. What would experienced Python programmers point out?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3661,7 +3677,8 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>```python
+          <t>A club treasurer wants to find whichever member paid the highest dues, by picking the record with the maximum contribution amount.
+```python
 members = [("Asha", 300), ("Ravi", 150), ("Meera", 450)]
 result = max(members, key=lambda m: m[1])
 ```
@@ -3743,7 +3760,8 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>```python
+          <t>A billing app calculates an invoice total with tax added, using a tax rate defined in the outer function and referenced from a nested helper function.
+```python
 def print_invoice(buyer):
     tax_rate = 0.05
     def add_tax(amount):
@@ -3829,7 +3847,8 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>```python
+          <t>A visitor-counting app on a museum's entry gate increments a shared counter each time someone walks in, using a function that modifies a variable defined outside it.
+```python
 counter = 0
 def increment():
     global counter
@@ -3916,7 +3935,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A developer writes a loop with a flag variable set to `True`, looping through a list and flipping the flag to `False` the moment one item fails a check, just to confirm every item passes. What single built-in call replaces this entire pattern?</t>
+          <t>A quiz app checks every answer in a list against a passing threshold using a flag variable flipped inside a loop, just to confirm every item passes. What single built-in call replaces this entire pattern?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3994,7 +4013,8 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>```python
+          <t>A museum's visitor counter function tries to increment a shared counter variable but forgets to declare it as global inside the function.
+```python
 counter = 0
 def increment():
     counter = counter + 1
@@ -4078,7 +4098,8 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>```python
+          <t>A ride-hailing app has a status variable defined at the global, enclosing, and local level all at once, and a developer wants to trace exactly what gets printed at each level.
+```python
 value = "global"
 def outer():
     value = "enclosing"

--- a/content/Question Bank/MCQ/Unit 8 - Functions/Unit 8 - Functions - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Unit 8 - Functions/Unit 8 - Functions - MCQ.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Python - MCQ - 8.1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Python - MCQ - 8.2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Python - MCQ - 8.3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Python - MCQ - 8.4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 8.1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 8.2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 8.3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 8.4" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -643,26 +643,26 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>Decomposition, breaking a big problem into smaller named pieces</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Looping, repeating one block of code many times</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>Recursion, calling the function from within itself</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Looping, repeating one block of code many times</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>Global scope, where every variable lives at the top level</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Decomposition, breaking a big problem into smaller named pieces</t>
-        </is>
-      </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -727,26 +727,26 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>An error, since service_charge is required</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>300.0</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>1200.0</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>An error, since service_charge is required</t>
-        </is>
-      </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -810,21 +810,21 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
+          <t>To deliberately hide a single-purpose helper that only that one function needs</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Because nested functions run faster than top-level ones</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>Because Python requires every function to be nested inside another</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Because nested functions run faster than top-level ones</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>To deliberately hide a single-purpose helper that only that one function needs</t>
-        </is>
-      </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -891,26 +891,26 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>`n == 1` is the base case, prints 24</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>There is no base case here, prints 24</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>`n == 1` is the base case, prints 24</t>
-        </is>
-      </c>
       <c r="O5" t="inlineStr">
         <is>
+          <t>`n == 1` is the base case, prints 4</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
           <t>`n == 0` is the base case, prints 24</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>`n == 1` is the base case, prints 4</t>
-        </is>
-      </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -975,26 +975,26 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>Naveen is the treasurer</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>role is the name</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>An error, since the order does not match the definition</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Naveen is the treasurer</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>treasurer is the Naveen</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>role is the name</t>
-        </is>
-      </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -1058,17 +1058,17 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>[('Asha', 300), ('Ravi', 150), ('Meera', 450)]</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>An error, since lambda cannot be used as a key</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>[('Meera', 450), ('Asha', 300), ('Ravi', 150)]</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>[('Asha', 300), ('Ravi', 150), ('Meera', 450)]</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1141,26 +1141,26 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>60, no import needed since it is a built-in</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>60, imported from functools</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>An error, reduce requires three arguments</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>30, imported from itertools</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>60, no import needed since it is a built-in</t>
-        </is>
-      </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -1223,26 +1223,26 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>`sum(overdue)`, returns `True`</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>`all(overdue)`, returns `True`</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>`any(overdue)`, returns `True`</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
           <t>`any(overdue)`, returns `False`</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>`any(overdue)`, returns `True`</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>`all(overdue)`, returns `True`</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>`sum(overdue)`, returns `True`</t>
-        </is>
-      </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -1306,21 +1306,21 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
+          <t>The logic needs multiple statements/branches, which a single-expression lambda cannot hold</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>Lambdas technically cannot ever take more than one single input</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>The logic needs multiple statements/branches, which a single-expression lambda cannot hold</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lambdas technically cannot ever be assigned to a variable at all</t>
+          <t>Lambdas technically cannot ever be assigned to a variable name at all, ever, by design</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1390,21 +1390,21 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
+          <t>It runs forever with no error, consuming all memory silently</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>It raises a `SyntaxError` before running</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>It raises a `RecursionError` once Python's call depth limit is reached</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>It runs forever with no error, consuming all memory silently</t>
-        </is>
-      </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1564,26 +1564,26 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>It technically removes the need for any variables at all</t>
+          <t>It makes a program run successfully without any input</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
+          <t>It technically removes the need for any variables at all in the script</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>It automatically and reliably makes the code run faster</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>It lets you write logic once and reuse it by name everywhere it is needed</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>It makes a program run successfully without any input</t>
-        </is>
-      </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -1642,26 +1642,26 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>function `greet()`:</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>define `greet()`:</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>def `greet()`:</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>function `greet()`:</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>`greet()` def:</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -1726,26 +1726,26 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>Nothing is printed, this raises an error</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Script finished.</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>Welcome!</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>Welcome! then Script finished.</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Nothing is printed, this raises an error</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Script finished.</t>
-        </is>
-      </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -1810,26 +1810,26 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>name is the parameter and "Asha" is the argument</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Both name and "Asha" are parameters</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>name is the argument and "Asha" is the parameter</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Both name and "Asha" are parameters</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>name is the parameter and "Asha" is the argument</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Both name and "Asha" are arguments</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -1888,26 +1888,26 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>An empty string</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>It raises an error</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
           <t>`None`</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>An empty string</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>It raises an error</t>
-        </is>
-      </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -1966,26 +1966,26 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>One or more copies can easily be missed or mis-edited, leaving inconsistent behaviour</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>It uses significantly more memory than necessary at runtime</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>The program will technically not run at all in this case</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>It uses significantly more memory than necessary at runtime</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>One or more copies can easily be missed or mis-edited, leaving inconsistent behaviour</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Python technically forbids having duplicate code blocks like this</t>
+          <t>Python technically forbids having duplicate code blocks like this anywhere</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -2050,26 +2050,26 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>It prints the word 'Hello!' completely normally as expected</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>It raises a `SyntaxError` before running anything</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>It raises a `NameError` because say_hello is not yet defined when called</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>It silently does absolutely nothing at all here</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>It prints the word 'Hello!' completely normally as expected</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>It raises a `NameError` because say_hello is not yet defined when called</t>
-        </is>
-      </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -2135,26 +2135,26 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>`None`</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Nothing is printed</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
           <t>An error is raised</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Nothing is printed</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>`None`</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -2213,26 +2213,26 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>The captured result is `None`, so later use of it fails or misbehaves</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
           <t>The later calculation uses the printed value automatically</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Python raises a `SyntaxError` at definition time</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>The captured result is `None`, so later use of it fails or misbehaves</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>The function call itself fails immediately</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -2302,21 +2302,21 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
+          <t>1500, and amounts is a tuple</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>An error, since *args cannot be summed</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
           <t>1500, and amounts is a list</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>1500, and amounts is a tuple</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>An error, since *args cannot be summed</t>
-        </is>
-      </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2483,14 +2483,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>['name', 'year']</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>{'name': 'Naveen', 'year': 2}</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>['name', 'year']</t>
-        </is>
-      </c>
       <c r="O2" t="inlineStr">
         <is>
           <t>('Naveen', 2)</t>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -2561,26 +2561,26 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>`lambda(x)`: x * x</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>lambda x: x * x</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>lambda x: return x * x</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>`lambda(x)`: x * x</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>def lambda x: x * x</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -2644,17 +2644,17 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>It silently treats the people parameter as also defaulting to 0 automatically</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>It technically raises a `NameError` only when it is called</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>It works exactly the same way as the default-last version</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>It silently treats the people parameter as also defaulting to 0</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -2731,21 +2731,21 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>It technically fails because total cannot be used as a keyword name here</t>
+          <t>It does not fail at all, this is perfectly valid Python</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
+          <t>It technically fails because total cannot be used as a keyword name in this call</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
           <t>It fails because a positional argument cannot follow a keyword argument in the same call</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>It does not fail at all, this is perfectly valid Python</t>
-        </is>
-      </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -2804,26 +2804,26 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>def `f(x, *args, **kwargs)`:</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>def `f(**kwargs, *args, x)`:</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>def `f(**kwargs, x, *args)`:</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>def `f(x, *args, **kwargs)`:</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>def `f(**kwargs, *args, x)`:</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>def `f(*args, x, **kwargs)`:</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -2888,17 +2888,17 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
+          <t>It silently swaps the roles of the two parameters</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>It only ever fails once the function is actually called</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>It silently swaps the roles of the two parameters</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>It works out exactly as originally intended, with no issue</t>
+          <t>It works out exactly as originally intended, with absolutely no issue at all</t>
         </is>
       </c>
       <c r="Q7" t="n">
@@ -2966,22 +2966,22 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>[315.0, 157.5, 472.5]</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
           <t>[300, 150, 450]</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>[315.0, 157.5, 472.5]</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>A map object with no usable values</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>1.05</t>
         </is>
       </c>
       <c r="Q8" t="n">
@@ -3049,26 +3049,26 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>[315.0, 472.5, 210.0]</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>[315.0, 157.5, 472.5, 210.0]</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>An empty []</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
           <t>Just [157.5]</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>An empty []</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>[315.0, 157.5, 472.5, 210.0]</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>[315.0, 472.5, 210.0]</t>
-        </is>
-      </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -3132,26 +3132,26 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>An error</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>`None`</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>`False`</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>`None`</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>`True`</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>An error</t>
-        </is>
-      </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -3219,22 +3219,22 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>It raises a `SyntaxError` immediately back at definition time</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
           <t>It silently does nothing at all and the script ends completely normally</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>It raises a `NameError`, since format_currency only exists inside print_receipt</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>It prints 'Rs 150.00' back again a second time here</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>It raises a `NameError`, since format_currency only exists inside print_receipt</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>It raises a `SyntaxError` immediately back at definition time</t>
         </is>
       </c>
       <c r="Q11" t="n">
@@ -3406,26 +3406,26 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>It raises a `NameError`, since total was local to the function</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>It simply prints the value `None` instead of a number</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>It prints the number 450 directly, as if nothing happened</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>It prints an entirely empty value back to the screen</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>It raises a `NameError`, since total was local to the function</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>It simply prints the value `None` instead of a number</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>It prints the number 450 directly, as if nothing happened</t>
-        </is>
-      </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -3491,26 +3491,26 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>('Asha', 'Ravi') then {'venue': 'Hall'}</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>{'Asha': 'Ravi'} then ('venue', 'Hall')</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>An error, since attendees has no fixed size</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>{'Asha': 'Ravi'} then ('venue', 'Hall')</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>('Fest', 'Asha', 'Ravi') then {}</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>('Asha', 'Ravi') then {'venue': 'Hall'}</t>
-        </is>
-      </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -3569,26 +3569,26 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>Lambdas technically always run slower than regular def functions</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Lambdas technically cannot accept more than one single parameter</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>Python has no actual restriction here, both can hold any logic</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>A lambda is limited to a single expression, not multiple statements or loops</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Lambdas technically always run slower than regular def functions</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Lambdas technically cannot accept more than one single parameter</t>
-        </is>
-      </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -3647,26 +3647,26 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>reduce and sum actually produce noticeably different results for the exact same list</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>`sum()` does the same job more simply, and reduce should be reserved for less common combinations</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>`map()` should technically have been used here instead of reduce</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>reduce is technically required here since `sum()` cannot add up a list</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>reduce and sum actually produce different results for the exact same list</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>`sum()` does the same job more simply, and reduce should be reserved for less common combinations</t>
-        </is>
-      </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -3730,26 +3730,26 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>Just 450</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Just Meera</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>('Asha', 300)</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>('Meera', 450)</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Just Meera</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Just 450</t>
-        </is>
-      </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -3817,22 +3817,22 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>tax_rate is automatically made global, so any function anywhere can see it</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>A nested function can read its enclosing function's local variables directly</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>Python implicitly passes tax_rate as a hidden parameter</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>A nested function can read its enclosing function's local variables directly</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>It cannot; this code raises a `NameError`</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>tax_rate is automatically global, so any function can see it</t>
         </is>
       </c>
       <c r="Q7" t="n">
@@ -3910,21 +3910,21 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
+          <t>An error, since global cannot be used this way</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>An error, since global cannot be used this way</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -3983,26 +3983,26 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>`sum(sequence)` &gt; 0</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>`all(sequence)`</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>`any(sequence)`</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
           <t>`len(sequence)` == 0</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>`sum(sequence)` &gt; 0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>`all(sequence)`</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>`any(sequence)`</t>
-        </is>
-      </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -4068,26 +4068,26 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>It raises an error, because assigning to counter makes it local before it has a value</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
           <t>It silently does nothing at all and counter simply stays at 0</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>It raises a `NameError` because counter was technically never defined anywhere</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
         <is>
           <t>The variable counter becomes 1 globally after this call</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>It raises a `NameError` because counter was never defined anywhere</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>It raises an error, because assigning to counter makes it local before it has a value</t>
-        </is>
-      </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -4164,17 +4164,17 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
+          <t>global, global, global</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>local, enclosing, global</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
           <t>global, enclosing, local</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>local, enclosing, global</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>global, global, global</t>
         </is>
       </c>
       <c r="Q11" t="n">

--- a/content/Question Bank/MCQ/Unit 8 - Functions/Unit 8 - Functions - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Unit 8 - Functions/Unit 8 - Functions - MCQ.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A program that calculates an entire trip budget is broken into split_cost, add_service_charge, and format_receipt instead of one giant block. What habit does this reflect?</t>
+          <t>A program that calculates an entire trip budget is broken into `split_cost`, `add_service_charge`, and `format_receipt` instead of one giant block. What habit does this reflect?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Since the call omits service_charge, Python uses its default value of 0, so the result is (1200 + 0) / 4, which is 300.0.</t>
+          <t>Since the call omits `service_charge`, Python uses its default value of 0, so the result is (1200 + 0) / 4, which is 300.0.</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -727,7 +727,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>An error, since service_charge is required</t>
+          <t>An error, since `service_charge` is required</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Why would a developer define format_currency inside print_receipt instead of at the top level of the script?</t>
+          <t>Why would a developer define `format_currency` inside `print_receipt` instead of at the top level of the script?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Without a base case to stop the chain, broken_factorial keeps calling itself with smaller and smaller n forever, with no condition ever returning directly; Python eventually hits its limit on call nesting depth and raises a `RecursionError`.</t>
+          <t>Without a base case to stop the chain, `broken_factorial` keeps calling itself with smaller and smaller n forever, with no condition ever returning directly; Python eventually hits its limit on call nesting depth and raises a `RecursionError`.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>It raises a `NameError` because say_hello is not yet defined when called</t>
+          <t>It raises a `NameError` because `say_hello` is not yet defined when called</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>add_no_return only prints its sum as a side effect and never returns a value, so Python automatically gives back `None`; result is therefore `None`, not 7.</t>
+          <t>`add_no_return` only prints its sum as a side effect and never returns a value, so Python automatically gives back `None`; result is therefore `None`, not 7.</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>It technically fails because split_cost requires exactly two arguments</t>
+          <t>It technically fails because `split_cost` requires exactly two arguments</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>format_currency is a nested function, defined and visible only inside print_receipt; calling it directly from outside raises a `NameError` because it does not exist in that outer scope.</t>
+          <t>`format_currency` is a nested function, defined and visible only inside `print_receipt`; calling it directly from outside raises a `NameError` because it does not exist in that outer scope.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>It raises a `NameError`, since format_currency only exists inside print_receipt</t>
+          <t>It raises a `NameError`, since `format_currency` only exists inside `print_receipt`</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>total is a local variable, created when calculate_total runs and destroyed the moment it returns; it never existed at the top level, so printing it there raises a `NameError`.</t>
+          <t>total is a local variable, created when `calculate_total` runs and destroyed the moment it returns; it never existed at the top level, so printing it there raises a `NameError`.</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -3769,7 +3769,7 @@
     print(add_tax(1000))
 print_invoice("Naveen")
 ```
-How does add_tax access tax_rate even though it was never passed in as a parameter?</t>
+How does `add_tax` access `tax_rate` even though it was never passed in as a parameter?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>tax_rate is automatically made global, so any function anywhere can see it</t>
+          <t>`tax_rate` is automatically made global, so any function anywhere can see it</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Python implicitly passes tax_rate as a hidden parameter</t>
+          <t>Python implicitly passes `tax_rate` as a hidden parameter</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">

--- a/content/Question Bank/MCQ/Unit 8 - Functions/Unit 8 - Functions - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Unit 8 - Functions/Unit 8 - Functions - MCQ.xlsx
@@ -1594,7 +1594,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A developer building a chat app wants to write a simple greet function that runs with no inputs at all, just to print a welcome banner when the app opens. Which line correctly starts a function definition named greet that takes no parameters?</t>
+          <t>A developer building a chat app wants to write a simple greet function that runs with no inputs at all, just to print a welcome banner when the app opens. Which line correctly starts a function definition named `greet` that takes no parameters?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A club membership app defines a function that welcomes a new member by name, then immediately calls it for a member named Asha.
+          <t>A club membership app defines a function that is supposed to welcome a new member by name.
 ```python
 def greet_member():
     print("Welcome!")
@@ -2513,7 +2513,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A math tutoring app needs a one-line helper to square any number a student enters, without writing a full function definition for something this small. Which lambda correctly squares its input, equivalent to def `square(x)`: return x * x?</t>
+          <t>A math tutoring app needs a one-line helper to square any number a student enters, without writing a full function definition for something this small. Which lambda correctly squares its input, equivalent to `def square(x): return x * x`?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2834,8 +2834,8 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A reporting tool's developer defines a function meant to accept ordinary fields plus flexible extras, but writes the **kwargs collector before the *args collector by mistake.
-A developer writes def `report(**details, *items)`: and expects it to work like ordinary parameters followed by *args then **kwargs. What actually happens?</t>
+          <t>A reporting tool's developer defines a function meant to accept ordinary fields plus flexible extras, but writes the `**kwargs` collector before the `*args` collector by mistake.
+A developer writes `def report(**details, *items):` and expects it to work like ordinary parameters followed by `*args` then `**kwargs`. What actually happens?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A finance app developer uses from functools import reduce and `reduce(lambda a, b: a + b, numbers)` purely to add up a list of monthly expenses. What would experienced Python programmers point out?</t>
+          <t>A finance app developer uses `from functools import reduce` and `reduce(lambda a, b: a + b, numbers)` purely to add up a list of monthly expenses. What would experienced Python programmers point out?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">

--- a/content/Question Bank/MCQ/Unit 8 - Functions/Unit 8 - Functions - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Unit 8 - Functions/Unit 8 - Functions - MCQ.xlsx
@@ -2,57 +2,113 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - Unit 8" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -124,6 +180,31 @@
 </styleSheet>
 </file>
 
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Unit8MCQTable" displayName="Unit8MCQTable" ref="A1:Q41" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <tableColumns count="17">
+    <tableColumn id="1" name="title"/>
+    <tableColumn id="2" name="description"/>
+    <tableColumn id="3" name="explanation"/>
+    <tableColumn id="4" name="score"/>
+    <tableColumn id="5" name="status"/>
+    <tableColumn id="6" name="difficulty"/>
+    <tableColumn id="7" name="bloomTaxonomy"/>
+    <tableColumn id="8" name="tags"/>
+    <tableColumn id="9" name="subjects"/>
+    <tableColumn id="10" name="topics"/>
+    <tableColumn id="11" name="subTopics"/>
+    <tableColumn id="12" name="companies"/>
+    <tableColumn id="13" name="option1"/>
+    <tableColumn id="14" name="option2"/>
+    <tableColumn id="15" name="option3"/>
+    <tableColumn id="16" name="option4"/>
+    <tableColumn id="17" name="answer"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -167,72 +248,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -288,7 +311,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -297,13 +320,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -337,17 +360,6 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -402,8 +414,6 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -415,179 +425,199 @@
   </sheetPr>
   <dimension ref="A1:Q41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="68" customWidth="1" min="2" max="2"/>
+    <col width="68" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="42" customWidth="1" min="13" max="13"/>
+    <col width="42" customWidth="1" min="14" max="14"/>
+    <col width="42" customWidth="1" min="15" max="15"/>
+    <col width="42" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>explanation</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>difficulty</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="11" t="inlineStr">
         <is>
           <t>bloomTaxonomy</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="11" t="inlineStr">
         <is>
           <t>tags</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="11" t="inlineStr">
         <is>
           <t>subjects</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="11" t="inlineStr">
         <is>
           <t>topics</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="11" t="inlineStr">
         <is>
           <t>subTopics</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="11" t="inlineStr">
         <is>
           <t>companies</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="11" t="inlineStr">
         <is>
           <t>option1</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="11" t="inlineStr">
         <is>
           <t>option2</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="11" t="inlineStr">
         <is>
           <t>option3</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="11" t="inlineStr">
         <is>
           <t>option4</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="11" t="inlineStr">
         <is>
           <t>answer</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="39.59999847412109" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Python - MCQ - 8.1.1</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>A program that calculates an entire trip budget is broken into `split_cost`, `add_service_charge`, and `format_receipt` instead of one giant block. What habit does this reflect?</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Decomposition is breaking a big problem into smaller, named pieces, each small enough to write, test, and trust on its own, rather than reasoning about one overwhelming block of code.</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="D2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>understand</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>python - Set 1</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>python</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>functions</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
         <is>
           <t>defining-and-calling-functions</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="L2" s="4" t="n"/>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Global scope, where every variable lives at the top level — this describes scope, not the decomposition habit of splitting logic into smaller named functions</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Recursion, calling the function from within itself</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
         <is>
           <t>Decomposition, breaking a big problem into smaller named pieces</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Recursion, calling the function from within itself</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Global scope, where every variable lives at the top level</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="P2" s="5" t="inlineStr">
         <is>
           <t>Looping, repeating one block of code many times</t>
         </is>
       </c>
-      <c r="Q2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="Q2" s="4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" ht="118.8000030517578" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Python - MCQ - 8.1.2</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>A trip organizer splits a shared bill among friends, and most trips have no extra service charge, but some do.
 ```python
@@ -598,160 +628,162 @@
 What is the result?</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Since the call omits `service_charge`, Python uses its default value of 0, so the result is (1200 + 0) / 4, which is 300.0.</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="D3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>function-parameters-and-arguments</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="n"/>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr">
+        <is>
+          <t>An error, since `service_charge` is required</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" ht="39.59999847412109" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Python - MCQ - 8.1.3</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Why would a developer define `format_currency` inside `print_receipt` instead of at the top level of the script?</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Nesting signals that the helper exists purely to support that one outer function and nobody else needs to call it directly, keeping the top level of the script focused on pieces that genuinely matter elsewhere.</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>apply</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>understand</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>python - Set 1</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>python</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>functions</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>function-parameters-and-arguments</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>1200.0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>An error, since `service_charge` is required</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Python - MCQ - 8.1.3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Why would a developer define `format_currency` inside `print_receipt` instead of at the top level of the script?</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Nesting signals that the helper exists purely to support that one outer function and nobody else needs to call it directly, keeping the top level of the script focused on pieces that genuinely matter elsewhere.</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>easy</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>understand</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>python - Set 1</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>python</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>functions</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>variable-scope-and-legb</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="L4" s="4" t="n"/>
+      <c r="M4" s="5" t="inlineStr">
         <is>
           <t>Because nested functions run faster than top-level ones</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>Because Python requires every function to be nested inside another — invents a nesting rule that doesn't exist in Python function definitions</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>Because top-level functions are not allowed to take parameters</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="inlineStr">
         <is>
           <t>To deliberately hide a single-purpose helper that only that one function needs</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Because top-level functions are not allowed to take parameters</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Because Python requires every function to be nested inside another</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="Q4" s="4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" ht="145.1999969482422" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Python - MCQ - 8.1.4</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>A student is asked to compute 4! by hand and notices the answer for any n depends on the answer for n-1, so they write it as a recursive function instead of a loop.
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>A developer is asked to compute 4! by hand and notices the answer for any n depends on the answer for n-1, so they write it as a recursive function instead of a loop.
 ```python
 def factorial(n):
     if n == 1:
@@ -762,80 +794,81 @@
 What is the base case here, and what is printed?</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>The base case is `n == 1`, which stops the recursive calls and returns 1 directly; the recursive step multiplies n by `factorial(n-1)`, unwinding to give 4 * 3 * 2 * 1, which is 24.</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="D5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>python - Set 1</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>python</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>functions</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>recursion</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="L5" s="4" t="n"/>
+      <c r="M5" s="5" t="inlineStr">
         <is>
           <t>`n == 1` is the base case, prints 24</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N5" s="5" t="inlineStr">
         <is>
           <t>There is no base case here, prints 24</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O5" s="5" t="inlineStr">
         <is>
           <t>`n == 0` is the base case, prints 24</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P5" s="5" t="inlineStr">
         <is>
           <t>`n == 1` is the base case, prints 4</t>
         </is>
       </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="Q5" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" ht="118.8000030517578" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Python - MCQ - 8.1.5</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>A club membership app introduces a member by name and role, and a developer calls the function while typing the role first out of habit.
 ```python
@@ -846,80 +879,81 @@
 What is printed?</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Keyword arguments are matched to parameters by name, not position, so naming both arguments explicitly correctly prints 'Naveen is the treasurer' regardless of the order they are written in the call.</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="D6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>understand</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>python - Set 1</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>python</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>functions</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>function-parameters-and-arguments</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="L6" s="4" t="n"/>
+      <c r="M6" s="5" t="inlineStr">
         <is>
           <t>Naveen is the treasurer</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N6" s="5" t="inlineStr">
         <is>
           <t>role is the name</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O6" s="5" t="inlineStr">
         <is>
           <t>treasurer is the Naveen</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P6" s="5" t="inlineStr">
         <is>
           <t>An error, since the order does not match the definition</t>
         </is>
       </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="Q6" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" ht="92.40000152587891" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Python - MCQ - 8.1.6</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>A treasurer has a list of members with their dues and wants them ranked from the smallest amount owed to the largest, without writing a separate named function just for sorting.
 ```python
@@ -929,80 +963,81 @@
 What does result contain?</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>The lambda tells `sorted()` to compare each tuple by its second element, the amount, so the list is sorted by amount ascending: Ravi (150), Asha (300), Meera (450).</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="D7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>python - Set 1</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>python</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>functions</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>lambda-functions</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>[('Meera', 450), ('Asha', 300), ('Ravi', 150)]</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
+      <c r="L7" s="4" t="n"/>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>[('Meera', 450), ('Asha', 300), ('Ravi', 150)] — this sorts in descending order instead of the ascending order sorted() actually produces</t>
+        </is>
+      </c>
+      <c r="N7" s="5" t="inlineStr">
         <is>
           <t>An error, since lambda cannot be used as a key</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O7" s="5" t="inlineStr">
         <is>
           <t>[('Asha', 300), ('Ravi', 150), ('Meera', 450)]</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P7" s="5" t="inlineStr">
         <is>
           <t>[('Ravi', 150), ('Asha', 300), ('Meera', 450)]</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="Q7" s="4" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="8" ht="92.40000152587891" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Python - MCQ - 8.1.7</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>A developer wants to collapse a list of contribution amounts into a single running total using functools instead of a manual loop.
 ```python
@@ -1012,80 +1047,81 @@
 What is result, and what module must be imported to use reduce?</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>reduce combines items two at a time, starting with 10 and 20 to get 30, then combining that with 30 to get 60; reduce is not a built-in like map and filter, it must be imported from functools.</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="D8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>python - Set 1</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>python</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>functions</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>higher-order-functions</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="L8" s="4" t="n"/>
+      <c r="M8" s="5" t="inlineStr">
         <is>
           <t>An error, reduce requires three arguments</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N8" s="5" t="inlineStr">
         <is>
           <t>60, imported from functools</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="O8" s="5" t="inlineStr">
         <is>
           <t>30, imported from itertools</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P8" s="5" t="inlineStr">
         <is>
           <t>60, no import needed since it is a built-in</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="Q8" s="4" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="9" ht="92.40000152587891" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Python - MCQ - 8.1.8</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>A club treasurer tracks whether each member's dues are overdue and wants a one-line check for whether at least one member still owes money.
 ```python
@@ -1094,80 +1130,81 @@
 Which function call correctly checks whether at least one member is overdue, and what does it return?</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>`any()` returns `True` if at least one item in the sequence is truthy; `any(overdue)` returns `True` here because one item is `True`, whereas `all()` would ask whether every item is truthy instead.</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="D9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>understand</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>python - Set 1</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>python</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>functions</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>built-in-functions</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="L9" s="4" t="n"/>
+      <c r="M9" s="5" t="inlineStr">
         <is>
           <t>`sum(overdue)`, returns `True`</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N9" s="5" t="inlineStr">
         <is>
           <t>`any(overdue)`, returns `True`</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="O9" s="5" t="inlineStr">
         <is>
           <t>`any(overdue)`, returns `False`</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P9" s="5" t="inlineStr">
         <is>
           <t>`all(overdue)`, returns `True`</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q9" s="4" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="10" ht="132" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Python - MCQ - 8.1.9</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>An event registration function needs to accept the event name, any number of attendee names, and any number of extra named details like the venue, all in one call.
 ```python
@@ -1179,80 +1216,81 @@
 What is printed?</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>event captures "Fest" positionally, every remaining positional argument falls into the attendees tuple as ('Asha', 'Ravi'), and the keyword argument becomes the details dictionary {'venue': 'Hall'}.</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="D10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>python - Set 1</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>python</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>functions</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
         <is>
           <t>function-parameters-and-arguments</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="L10" s="4" t="n"/>
+      <c r="M10" s="5" t="inlineStr">
         <is>
           <t>An error, since attendees has no fixed size</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N10" s="5" t="inlineStr">
         <is>
           <t>('Fest', 'Asha', 'Ravi') then {}</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="O10" s="5" t="inlineStr">
         <is>
           <t>{'Asha': 'Ravi'} then ('venue', 'Hall')</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P10" s="5" t="inlineStr">
         <is>
           <t>('Asha', 'Ravi') then {'venue': 'Hall'}</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q10" s="4" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="11" ht="118.8000030517578" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Python - MCQ - 8.1.10</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>A payroll script needs 5! (factorial of 5) for a bonus calculation, so a developer writes a recursive function but forgets to give it a stopping condition.
 ```python
@@ -1263,158 +1301,160 @@
 Why does this eventually fail, and what does Python raise?</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Without a base case to stop the chain, `broken_factorial` keeps calling itself with smaller and smaller n forever, with no condition ever returning directly; Python eventually hits its limit on call nesting depth and raises a `RecursionError`.</t>
         </is>
       </c>
-      <c r="D11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="D11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>python - Set 1</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>python</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>functions</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>recursion</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="L11" s="4" t="n"/>
+      <c r="M11" s="5" t="inlineStr">
         <is>
           <t>It raises a `SyntaxError` before running</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>It runs forever with no error, consuming all memory silently</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>It runs forever with no error, consuming all memory silently — recursion depth is bounded, so Python raises RecursionError long before memory runs out</t>
+        </is>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
         <is>
           <t>It raises a `RecursionError` once Python's call depth limit is reached</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P11" s="5" t="inlineStr">
         <is>
           <t>It returns `None` because n eventually becomes 0</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q11" s="4" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="12" ht="39.59999847412109" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Python - MCQ - 8.2.1</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>A developer writes a 5-line validation routine with two if/elif branches entirely as one lambda assigned to a variable, then complains it raises a `SyntaxError`. What is the actual problem?</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>A lambda body must be a single expression; it cannot hold multiple statements or branching logic across several lines, so this kind of multi-branch routine belongs in a regular def function instead.</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="D12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>python</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>functions</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
         <is>
           <t>lambda-functions</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="L12" s="4" t="n"/>
+      <c r="M12" s="5" t="inlineStr">
         <is>
           <t>Lambdas cannot take more than one parameter</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N12" s="5" t="inlineStr">
         <is>
           <t>The logic needs multiple statements/branches, which a single-expression lambda cannot hold</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>The variable's name directly conflicts with the lambda keyword</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
+      <c r="O12" s="5" t="inlineStr">
+        <is>
+          <t>The variable's name directly conflicts with the lambda keyword — lambda is a keyword for the function itself, not a naming restriction on variables</t>
+        </is>
+      </c>
+      <c r="P12" s="5" t="inlineStr">
         <is>
           <t>Lambdas cannot be assigned to a variable name</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="Q12" s="4" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="13" ht="105.5999984741211" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Python - MCQ - 8.2.2</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>A developer writes a short description right under a function's def line so teammates can understand its purpose later.
 ```python
@@ -1425,158 +1465,160 @@
 What is this triple-quoted description called?</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>A triple-quoted string placed as the first line of a function body is its docstring — the built-in documentation that tools like help() display.</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="D13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>remember</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>python</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>functions</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
         <is>
           <t>defining-and-calling-functions</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="L13" s="4" t="n"/>
+      <c r="M13" s="5" t="inlineStr">
         <is>
           <t>A docstring</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N13" s="5" t="inlineStr">
         <is>
           <t>An inline comment</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O13" s="5" t="inlineStr">
         <is>
           <t>A decorator</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="P13" s="5" t="inlineStr">
         <is>
           <t>A type hint</t>
         </is>
       </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="Q13" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" ht="39.59999847412109" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Python - MCQ - 8.2.3</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>A developer building a chat app wants to write a simple greet function that runs with no inputs at all, just to print a welcome banner when the app opens. Which line correctly starts a function definition named `greet` that takes no parameters?</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>A function definition begins with the def keyword, the function name, parentheses for parameters, and a colon, exactly mirroring how if and while blocks are written.</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="D14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>remember</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>python</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>functions</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
         <is>
           <t>defining-and-calling-functions</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="L14" s="4" t="n"/>
+      <c r="M14" s="5" t="inlineStr">
         <is>
           <t>`greet()` def:</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N14" s="5" t="inlineStr">
         <is>
           <t>function `greet()`:</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="O14" s="5" t="inlineStr">
         <is>
           <t>def `greet()`:</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="P14" s="5" t="inlineStr">
         <is>
           <t>define `greet()`:</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="Q14" s="4" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="15" ht="118.8000030517578" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Python - MCQ - 8.2.4</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>A club membership app defines a function that is supposed to welcome a new member by name.
 ```python
@@ -1587,80 +1629,81 @@
 What is printed when this code runs?</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Defining a function only teaches Python the recipe; it does not execute the body. Since `greet_member()` is never called, only the unconditional print statement runs, printing 'Script finished.'</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
+      <c r="D15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>python</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>functions</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
         <is>
           <t>defining-and-calling-functions</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="L15" s="4" t="n"/>
+      <c r="M15" s="5" t="inlineStr">
         <is>
           <t>Nothing is printed, this raises an error</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N15" s="5" t="inlineStr">
         <is>
           <t>Script finished.</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="O15" s="5" t="inlineStr">
         <is>
           <t>Welcome! then Script finished.</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="P15" s="5" t="inlineStr">
         <is>
           <t>Welcome!</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="Q15" s="4" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="16" ht="118.8000030517578" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Python - MCQ - 8.2.5</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>A chat app defines a greet function that takes a username and prints a welcome message when a new user logs in.
 ```python
@@ -1671,236 +1714,239 @@
 Which statement correctly distinguishes parameter and argument here?</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>name is the parameter, the placeholder named in the function definition, while "Asha" is the argument, the actual value supplied at the specific call.</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="D16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>understand</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>function-parameters-and-arguments</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="n"/>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>name is the argument and "Asha" is the parameter — this swaps the roles, name is actually the parameter and "Asha" the argument</t>
+        </is>
+      </c>
+      <c r="N16" s="5" t="inlineStr">
+        <is>
+          <t>Both name and "Asha" are parameters</t>
+        </is>
+      </c>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>Both name and "Asha" are arguments</t>
+        </is>
+      </c>
+      <c r="P16" s="5" t="inlineStr">
+        <is>
+          <t>name is the parameter and "Asha" is the argument</t>
+        </is>
+      </c>
+      <c r="Q16" s="4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" ht="39.59999847412109" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Python - MCQ - 8.2.6</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>A food delivery app has a function that logs an order but never explicitly returns anything, and another part of the code tries to use whatever the function "gives back". What value does a function return if it has no return statement at all?</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Every Python function returns something even without an explicit return statement; when none is written, the function automatically returns `None` once it finishes.</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>understand</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>remember</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>python</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>functions</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
         <is>
           <t>function-parameters-and-arguments</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>name is the argument and "Asha" is the parameter</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Both name and "Asha" are parameters</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>Both name and "Asha" are arguments</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>name is the parameter and "Asha" is the argument</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
+      <c r="L17" s="4" t="n"/>
+      <c r="M17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>It raises an error</t>
+        </is>
+      </c>
+      <c r="O17" s="5" t="inlineStr">
+        <is>
+          <t>An empty string</t>
+        </is>
+      </c>
+      <c r="P17" s="5" t="inlineStr">
+        <is>
+          <t>`None`</t>
+        </is>
+      </c>
+      <c r="Q17" s="4" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Python - MCQ - 8.2.6</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>A food delivery app has a function that logs an order but never explicitly returns anything, and another part of the code tries to use whatever the function "gives back". What value does a function return if it has no return statement at all?</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Every Python function returns something even without an explicit return statement; when none is written, the function automatically returns `None` once it finishes.</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>easy</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>remember</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
+    <row r="18" ht="39.59999847412109" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Python - MCQ - 8.2.7</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>A developer copy-pastes the same bill-splitting calculation into three different scripts for a trip-planning app. The formula later needs a service charge added. What is the main risk of this approach?</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Since the logic is duplicated, the developer must find and correctly edit every single copy; missing even one copy leaves a hidden bug, whereas a single function would only need one edit to fix every call.</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>python</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>functions</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>function-parameters-and-arguments</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>It raises an error</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>An empty string</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>`None`</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Python - MCQ - 8.2.7</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>A developer copy-pastes the same bill-splitting calculation into three different scripts for a trip-planning app. The formula later needs a service charge added. What is the main risk of this approach?</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Since the logic is duplicated, the developer must find and correctly edit every single copy; missing even one copy leaves a hidden bug, whereas a single function would only need one edit to fix every call.</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>analyze</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>python - Set 2</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>python</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>functions</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
         <is>
           <t>defining-and-calling-functions</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="L18" s="4" t="n"/>
+      <c r="M18" s="5" t="inlineStr">
         <is>
           <t>It uses significantly more memory than necessary at runtime</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="N18" s="5" t="inlineStr">
         <is>
           <t>The program will technically not run at all in this case</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="O18" s="5" t="inlineStr">
         <is>
           <t>One or more copies can easily be missed or mis-edited, leaving inconsistent behaviour</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Python technically forbids having duplicate code blocks like this anywhere</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
+      <c r="P18" s="5" t="inlineStr">
+        <is>
+          <t>Python technically forbids having duplicate code blocks like this anywhere — Python enforces no such rule, duplicated code just risks silently drifting out of sync</t>
+        </is>
+      </c>
+      <c r="Q18" s="4" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="19" ht="118.8000030517578" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Python - MCQ - 8.2.8</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>A club onboarding script calls its greeting function before the function has actually been defined anywhere in the file.
 ```python
@@ -1911,80 +1957,81 @@
 What happens when this code runs?</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Python reads top to bottom, so when it reaches the call `say_hello()` it has not yet processed the def below it, and the name does not exist yet, raising a `NameError`.</t>
         </is>
       </c>
-      <c r="D19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
+      <c r="D19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>python</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>functions</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>defining-and-calling-functions</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>It prints the word 'Hello!' completely normally as expected</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
+      <c r="L19" s="4" t="n"/>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>It prints the word 'Hello!' completely normally as expected — ignores that name lookup happens at call time, before the function is defined</t>
+        </is>
+      </c>
+      <c r="N19" s="5" t="inlineStr">
         <is>
           <t>It raises a `SyntaxError` before running anything</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="O19" s="5" t="inlineStr">
         <is>
           <t>It raises a `NameError` because `say_hello` is not yet defined when called</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="P19" s="5" t="inlineStr">
         <is>
           <t>It silently does absolutely nothing at all here</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="Q19" s="4" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="20" ht="132" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Python - MCQ - 8.2.9</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>A calculator app adds two numbers inside a function and prints the sum, but the caller also tries to capture and reuse the function's return value.
 ```python
@@ -1996,158 +2043,160 @@
 What is printed by the second print statement?</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>`add_no_return` only prints its sum as a side effect and never returns a value, so Python automatically gives back `None`; result is therefore `None`, not 7.</t>
         </is>
       </c>
-      <c r="D20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
+      <c r="D20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>python</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>functions</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>function-parameters-and-arguments</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="L20" s="4" t="n"/>
+      <c r="M20" s="5" t="inlineStr">
         <is>
           <t>An error is raised</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="N20" s="5" t="inlineStr">
         <is>
           <t>Nothing is printed</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="O20" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="P20" s="5" t="inlineStr">
         <is>
           <t>`None`</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="Q20" s="4" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="21" ht="39.59999847412109" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Python - MCQ - 8.2.10</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>A billing system writes `calculate_total(price, quantity)` expecting to use its result in a later calculation, but forgets to include a return statement, only printing the value inside the function. What happens when the result is used afterward?</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>Because the function never returns a value, the variable capturing its result holds `None` instead of the computed number, so any later arithmetic using that variable will fail or silently produce a wrong result involving `None`.</t>
         </is>
       </c>
-      <c r="D21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
+      <c r="D21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>python</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>functions</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
         <is>
           <t>function-parameters-and-arguments</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>The later calculation uses the printed value automatically</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
+      <c r="L21" s="4" t="n"/>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>The later calculation uses the printed value automatically — printing displays a value on screen but does not make it available to the caller</t>
+        </is>
+      </c>
+      <c r="N21" s="5" t="inlineStr">
         <is>
           <t>The captured result is `None`, so later use of it fails or misbehaves</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="O21" s="5" t="inlineStr">
         <is>
           <t>The function call itself fails immediately</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="P21" s="5" t="inlineStr">
         <is>
           <t>Python raises a `SyntaxError` at definition time</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q21" s="4" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="22" ht="118.8000030517578" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Python - MCQ - 8.2.11</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>A club treasurer wants a function that can accept any number of member contributions in one call and add them all up, without fixing the number of arguments in advance.
 ```python
@@ -2158,82 +2207,83 @@
 What is printed, and what type is amounts inside the function?</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>The single star gathers every positional argument into a tuple, so amounts becomes (500, 400, 600) inside the function, and `sum(amounts)` correctly returns 1500.</t>
         </is>
       </c>
-      <c r="D22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
+      <c r="D22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>remember</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>python</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>functions</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
         <is>
           <t>function-parameters-and-arguments</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="L22" s="4" t="n"/>
+      <c r="M22" s="5" t="inlineStr">
         <is>
           <t>500, and amounts is a dictionary</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="N22" s="5" t="inlineStr">
         <is>
           <t>An error, since *args cannot be summed</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="O22" s="5" t="inlineStr">
         <is>
           <t>1500, and amounts is a tuple</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="P22" s="5" t="inlineStr">
         <is>
           <t>1500, and amounts is a list</t>
         </is>
       </c>
-      <c r="Q22" t="n">
+      <c r="Q22" s="4" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="23" ht="132" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Python - MCQ - 8.2.12</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>A student registration form wants to accept any combination of optional profile fields, like name and year, without hardcoding each one as a separate parameter.
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>A user-registration form wants to accept any combination of optional profile fields, like name and year, without hardcoding each one as a separate parameter.
 ```python
 def build_profile(**details):
     return details
@@ -2243,158 +2293,160 @@
 What is printed?</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>Two stars gather every keyword argument into a dictionary, mapping each keyword to its value, so profile becomes {'name': 'Naveen', 'year': 2}.</t>
         </is>
       </c>
-      <c r="D23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
+      <c r="D23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>python</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>functions</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
         <is>
           <t>function-parameters-and-arguments</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="L23" s="4" t="n"/>
+      <c r="M23" s="5" t="inlineStr">
         <is>
           <t>['name', 'year']</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="N23" s="5" t="inlineStr">
         <is>
           <t>{'name': 'Naveen', 'year': 2}</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="O23" s="5" t="inlineStr">
         <is>
           <t>An error, since **kwargs needs a fixed number of names</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="P23" s="5" t="inlineStr">
         <is>
           <t>('Naveen', 2)</t>
         </is>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q23" s="4" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="24" ht="39.59999847412109" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Python - MCQ - 8.2.13</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>A math tutoring app needs a one-line helper to square any number a student enters, without writing a full function definition for something this small. Which lambda correctly squares its input, equivalent to `def square(x): return x * x`?</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>A math tutoring app needs a one-line helper to square any number a customer enters, without writing a full function definition for something this small. Which lambda correctly squares its input, equivalent to `def square(x): return x * x`?</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>A lambda is written as lambda parameters: expression, with the expression's value automatically returned; lambda x: x * x matches the def version exactly.</t>
         </is>
       </c>
-      <c r="D24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
+      <c r="D24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>remember</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>python</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>functions</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
         <is>
           <t>lambda-functions</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="L24" s="4" t="n"/>
+      <c r="M24" s="5" t="inlineStr">
         <is>
           <t>def lambda x: x * x</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="N24" s="5" t="inlineStr">
         <is>
           <t>lambda x: x * x</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="O24" s="5" t="inlineStr">
         <is>
           <t>lambda x: return x * x</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="P24" s="5" t="inlineStr">
         <is>
           <t>`lambda(x)`: x * x</t>
         </is>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q24" s="4" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="25" ht="92.40000152587891" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Python - MCQ - 8.2.14</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>A trip-planning app's bill-splitting function accidentally places a default-valued parameter before a required one when it's defined.
 ```python
@@ -2404,80 +2456,81 @@
 What happens when Python tries to process this definition?</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>Python requires every parameter with a default value to appear after every parameter without a default; here a non-default parameter, people, follows a defaulted one, which raises a `SyntaxError`.</t>
         </is>
       </c>
-      <c r="D25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
+      <c r="D25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>python</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>functions</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
         <is>
           <t>function-parameters-and-arguments</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="L25" s="4" t="n"/>
+      <c r="M25" s="5" t="inlineStr">
         <is>
           <t>It raises a `SyntaxError` because a non-default parameter follows a default one</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="N25" s="5" t="inlineStr">
         <is>
           <t>It works exactly the same way as the default-last version</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>It silently treats the people parameter as also defaulting to 0 automatically</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
+      <c r="O25" s="5" t="inlineStr">
+        <is>
+          <t>It silently treats the people parameter as also defaulting to 0 automatically — Python raises this error at definition time rather than silently applying a default</t>
+        </is>
+      </c>
+      <c r="P25" s="5" t="inlineStr">
         <is>
           <t>It technically raises a `NameError` only when it is called</t>
         </is>
       </c>
-      <c r="Q25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="Q25" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" ht="79.19999694824219" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Python - MCQ - 8.2.15</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>A trip-planning app calls its bill-splitting function while mixing a keyword argument with a positional one in the wrong order.
 ```python
@@ -2486,237 +2539,240 @@
 Why does this call fail?</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>Once a call starts naming an argument with a keyword, every argument after it must also be a keyword argument; here a positional argument, 4, appears after the keyword argument `total=1200`, which raises a `SyntaxError`.</t>
         </is>
       </c>
-      <c r="D26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
+      <c r="D26" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>python</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>functions</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
         <is>
           <t>function-parameters-and-arguments</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="L26" s="4" t="n"/>
+      <c r="M26" s="5" t="inlineStr">
         <is>
           <t>It fails because a positional argument cannot follow a keyword argument in the same call</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="N26" s="5" t="inlineStr">
         <is>
           <t>It technically fails because `split_cost` requires exactly two arguments</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>It technically fails because total cannot be used as a keyword name in this call</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
+      <c r="O26" s="5" t="inlineStr">
+        <is>
+          <t>It technically fails because total cannot be used as a keyword name in this call — total is a valid keyword name here, the real problem is the argument order</t>
+        </is>
+      </c>
+      <c r="P26" s="5" t="inlineStr">
         <is>
           <t>It does not fail at all, this is perfectly valid Python</t>
         </is>
       </c>
-      <c r="Q26" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="Q26" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" ht="52.79999923706055" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>Python - MCQ - 8.2.16</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>A reporting tool needs a function that accepts a few fixed fields, then any number of extra positional values, then any number of extra named values, all in one signature. Which parameter order is valid in a function definition that uses ordinary parameters, *args, and **kwargs together?</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>Python requires ordinary parameters first, then *args, then **kwargs, in that exact order; any other arrangement raises a `SyntaxError`.</t>
         </is>
       </c>
-      <c r="D27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
+      <c r="D27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>understand</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>python</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>functions</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
         <is>
           <t>function-parameters-and-arguments</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>def `f(**kwargs, x, *args)`:</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
+      <c r="L27" s="4" t="n"/>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>def `f(**kwargs, x, *args)`: — this places **kwargs before the positional and *args parameters, which Python disallows</t>
+        </is>
+      </c>
+      <c r="N27" s="5" t="inlineStr">
         <is>
           <t>def `f(x, *args, **kwargs)`:</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="O27" s="5" t="inlineStr">
         <is>
           <t>def `f(*args, x, **kwargs)`:</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="P27" s="5" t="inlineStr">
         <is>
           <t>def `f(**kwargs, *args, x)`:</t>
         </is>
       </c>
-      <c r="Q27" t="n">
+      <c r="Q27" s="4" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="28" ht="52.79999923706055" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Python - MCQ - 8.2.17</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>A reporting tool's developer defines a function meant to accept ordinary fields plus flexible extras, but writes the `**kwargs` collector before the `*args` collector by mistake.
 A developer writes `def report(**details, *items):` and expects it to work like ordinary parameters followed by `*args` then `**kwargs`. What actually happens?</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>Python enforces a strict order of ordinary parameters, then *args, then **kwargs in a definition; placing **kwargs before *args is invalid and raises a `SyntaxError` before the function can even be defined.</t>
         </is>
       </c>
-      <c r="D28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
+      <c r="D28" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H28" s="4" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>python</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>functions</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
         <is>
           <t>function-parameters-and-arguments</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>It works out exactly as originally intended, with absolutely no issue at all</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
+      <c r="L28" s="4" t="n"/>
+      <c r="M28" s="5" t="inlineStr">
+        <is>
+          <t>It works out exactly as originally intended, with absolutely no issue at all — **kwargs cannot precede *args in a definition, this raises a SyntaxError instead</t>
+        </is>
+      </c>
+      <c r="N28" s="5" t="inlineStr">
         <is>
           <t>It silently swaps the roles of the two parameters</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="O28" s="5" t="inlineStr">
         <is>
           <t>It only ever fails once the function is actually called</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="P28" s="5" t="inlineStr">
         <is>
           <t>It raises a `SyntaxError` because **kwargs cannot precede *args in the definition</t>
         </is>
       </c>
-      <c r="Q28" t="n">
+      <c r="Q28" s="4" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="29" ht="92.40000152587891" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>Python - MCQ - 8.2.18</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>A club treasurer wants to apply a 5% late fee to every member's outstanding dues in one line, without writing a manual loop.
 ```python
@@ -2726,80 +2782,81 @@
 What does result contain?</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>map applies the lambda to every item in dues individually, multiplying each by 1.05, producing [315.0, 157.5, 472.5].</t>
         </is>
       </c>
-      <c r="D29" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
+      <c r="D29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>remember</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H29" s="4" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>python</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>functions</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
         <is>
           <t>higher-order-functions</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="L29" s="4" t="n"/>
+      <c r="M29" s="5" t="inlineStr">
         <is>
           <t>[315.0, 157.5, 472.5]</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="N29" s="5" t="inlineStr">
         <is>
           <t>1.05</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="O29" s="5" t="inlineStr">
         <is>
           <t>[300, 150, 450]</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="P29" s="5" t="inlineStr">
         <is>
           <t>A map object with no usable values</t>
         </is>
       </c>
-      <c r="Q29" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="Q29" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" ht="92.40000152587891" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>Python - MCQ - 8.2.19</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>A finance app wants to flag only the transactions above Rs 200 out of a list of recent payment amounts, using a single filter call instead of a manual loop.
 ```python
@@ -2809,80 +2866,81 @@
 What does result contain?</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>filter keeps only the items for which the lambda returns `True`, so only values greater than 200 survive: [315.0, 472.5, 210.0].</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>easy</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
+      <c r="D30" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
         <is>
           <t>understand</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H30" s="4" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>python</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>functions</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
         <is>
           <t>higher-order-functions</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="L30" s="4" t="n"/>
+      <c r="M30" s="5" t="inlineStr">
         <is>
           <t>[315.0, 157.5, 472.5, 210.0]</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="N30" s="5" t="inlineStr">
         <is>
           <t>An empty []</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="O30" s="5" t="inlineStr">
         <is>
           <t>Just [157.5]</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="P30" s="5" t="inlineStr">
         <is>
           <t>[315.0, 472.5, 210.0]</t>
         </is>
       </c>
-      <c r="Q30" t="n">
+      <c r="Q30" s="4" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="31" ht="92.40000152587891" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>Python - MCQ - 8.2.20</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>A club treasurer tracks whether each member has paid their dues and wants a one-line check for whether everyone has paid.
 ```python
@@ -2892,80 +2950,81 @@
 What is printed?</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>`all()` returns `True` only if every item in the sequence is truthy; since one item is `False`, `all(paid)` returns `False`.</t>
         </is>
       </c>
-      <c r="D31" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
+      <c r="D31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t>remember</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H31" s="4" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>python</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>functions</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
         <is>
           <t>built-in-functions</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="L31" s="4" t="n"/>
+      <c r="M31" s="5" t="inlineStr">
         <is>
           <t>`None`</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="N31" s="5" t="inlineStr">
         <is>
           <t>`False`</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="O31" s="5" t="inlineStr">
         <is>
           <t>`True`</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="P31" s="5" t="inlineStr">
         <is>
           <t>An error</t>
         </is>
       </c>
-      <c r="Q31" t="n">
+      <c r="Q31" s="4" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="32" ht="158.3999938964844" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Python - MCQ - 8.2.21</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>A billing script defines a currency-formatting helper nested inside its receipt-printing function, then tries to call that helper directly from outside afterward.
 ```python
@@ -2979,80 +3038,81 @@
 What happens on the last line?</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>`format_currency` is a nested function, defined and visible only inside `print_receipt`; calling it directly from outside raises a `NameError` because it does not exist in that outer scope.</t>
         </is>
       </c>
-      <c r="D32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
+      <c r="D32" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H32" s="4" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>python</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>functions</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
         <is>
           <t>variable-scope-and-legb</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="L32" s="4" t="n"/>
+      <c r="M32" s="5" t="inlineStr">
         <is>
           <t>It raises a `SyntaxError` immediately back at definition time</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>It silently does nothing at all and the script ends completely normally</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
+      <c r="N32" s="5" t="inlineStr">
+        <is>
+          <t>It silently does nothing at all and the script ends completely normally — an undefined name at call time still raises an error, it doesn't fail silently</t>
+        </is>
+      </c>
+      <c r="O32" s="5" t="inlineStr">
         <is>
           <t>It raises a `NameError`, since `format_currency` only exists inside `print_receipt`</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="P32" s="5" t="inlineStr">
         <is>
           <t>It prints 'Rs 150.00' back again a second time here</t>
         </is>
       </c>
-      <c r="Q32" t="n">
+      <c r="Q32" s="4" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="33" ht="145.1999969482422" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>Python - MCQ - 8.2.22</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>A billing script computes an order's total inside a function and a later line outside the function tries to reuse that same total variable directly.
 ```python
@@ -3065,237 +3125,240 @@
 What happens on the last line?</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>total is a local variable, created when `calculate_total` runs and destroyed the moment it returns; it never existed at the top level, so printing it there raises a `NameError`.</t>
         </is>
       </c>
-      <c r="D33" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
+      <c r="D33" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>remember</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H33" s="4" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>python</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>functions</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
         <is>
           <t>variable-scope-and-legb</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>It prints the number 450 directly, as if nothing happened</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
+      <c r="L33" s="4" t="n"/>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>It prints the number 450 directly, as if nothing happened — total is local to the function and never leaks into the calling scope</t>
+        </is>
+      </c>
+      <c r="N33" s="5" t="inlineStr">
         <is>
           <t>It prints an entirely empty value back to the screen</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="O33" s="5" t="inlineStr">
         <is>
           <t>It raises a `NameError`, since total was local to the function</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="P33" s="5" t="inlineStr">
         <is>
           <t>It simply prints the value `None` instead of a number</t>
         </is>
       </c>
-      <c r="Q33" t="n">
+      <c r="Q33" s="4" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="34" ht="52.79999923706055" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>Python - MCQ - 8.2.23</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>A new teammate wants to read how a colleague's `split_cost` function should be used, directly from the Python interpreter. The function has a docstring under its def line.
 Which call displays that documentation?</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>`help(split_cost)` displays the function's docstring in the interpreter. The function is passed by name, without parentheses after it, so it is not called in the process.</t>
         </is>
       </c>
-      <c r="D34" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
+      <c r="D34" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" s="4" t="inlineStr">
         <is>
           <t>understand</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H34" s="4" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>python</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>functions</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
         <is>
           <t>defining-and-calling-functions</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="L34" s="4" t="n"/>
+      <c r="M34" s="5" t="inlineStr">
         <is>
           <t>`help(split_cost)`</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="N34" s="5" t="inlineStr">
         <is>
           <t>`split_cost()` — the docstring prints automatically on every call</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="O34" s="5" t="inlineStr">
         <is>
           <t>`split_cost.help()`</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="P34" s="5" t="inlineStr">
         <is>
           <t>`docstring(split_cost)`</t>
         </is>
       </c>
-      <c r="Q34" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="Q34" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" ht="39.59999847412109" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Python - MCQ - 8.2.24</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>A finance app developer uses `from functools import reduce` and `reduce(lambda a, b: a + b, numbers)` purely to add up a list of monthly expenses. What would experienced Python programmers point out?</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>For plain addition, the built-in `sum()` does exactly the same job with far less ceremony and no import; reduce is genuinely useful for combining logic that has no dedicated built-in, like multiplying everything together.</t>
         </is>
       </c>
-      <c r="D35" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
+      <c r="D35" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H35" s="4" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>python</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>functions</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
         <is>
           <t>higher-order-functions</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="L35" s="4" t="n"/>
+      <c r="M35" s="5" t="inlineStr">
         <is>
           <t>`sum()` does the same job more simply, and reduce should be reserved for less common combinations</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="N35" s="5" t="inlineStr">
         <is>
           <t>`map()` should technically have been used here instead of reduce</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>reduce and sum actually produce noticeably different results for the exact same list</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
+      <c r="O35" s="5" t="inlineStr">
+        <is>
+          <t>reduce and sum actually produce noticeably different results for the exact same list — for plain addition, reduce and sum() return exactly the same total</t>
+        </is>
+      </c>
+      <c r="P35" s="5" t="inlineStr">
         <is>
           <t>reduce is technically required here since `sum()` cannot add up a list</t>
         </is>
       </c>
-      <c r="Q35" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="Q35" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" ht="92.40000152587891" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>Python - MCQ - 8.2.25</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>A club treasurer wants to find whichever member paid the highest dues, by picking the record with the maximum contribution amount.
 ```python
@@ -3305,80 +3368,81 @@
 What is result?</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>The key function tells `max()` to compare each tuple by its second element, the amount; Meera's 450 is the largest amount, so max returns ('Meera', 450) as a whole tuple, not just the number.</t>
         </is>
       </c>
-      <c r="D36" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
+      <c r="D36" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G36" s="4" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H36" s="4" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>python</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>functions</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
         <is>
           <t>built-in-functions</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="L36" s="4" t="n"/>
+      <c r="M36" s="5" t="inlineStr">
         <is>
           <t>Just Meera</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="N36" s="5" t="inlineStr">
         <is>
           <t>Just 450</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>('Asha', 300)</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
+      <c r="O36" s="5" t="inlineStr">
+        <is>
+          <t>('Asha', 300) — this picks an arbitrary entry rather than the one with the maximum key value</t>
+        </is>
+      </c>
+      <c r="P36" s="5" t="inlineStr">
         <is>
           <t>('Meera', 450)</t>
         </is>
       </c>
-      <c r="Q36" t="n">
+      <c r="Q36" s="4" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+    <row r="37" ht="158.3999938964844" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>Python - MCQ - 8.2.26</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>A billing app calculates an invoice total with tax added, using a tax rate defined in the outer function and referenced from a nested helper function.
 ```python
@@ -3392,80 +3456,81 @@
 How does `add_tax` access `tax_rate` even though it was never passed in as a parameter?</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>A nested function can read variables from its enclosing function directly, without those variables being passed in as arguments, because it has access to the enclosing function's local scope.</t>
         </is>
       </c>
-      <c r="D37" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
+      <c r="D37" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G37" s="4" t="inlineStr">
         <is>
           <t>understand</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H37" s="4" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>python</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>functions</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
         <is>
           <t>variable-scope-and-legb</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="L37" s="4" t="n"/>
+      <c r="M37" s="5" t="inlineStr">
         <is>
           <t>A nested function can read its enclosing function's local variables directly</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>`tax_rate` is automatically made global, so any function anywhere can see it</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
+      <c r="N37" s="5" t="inlineStr">
+        <is>
+          <t>`tax_rate` is automatically made global, so any function anywhere can see it — tax_rate stays local to print_invoice and is reached through closure, not made global</t>
+        </is>
+      </c>
+      <c r="O37" s="5" t="inlineStr">
         <is>
           <t>It cannot; this code raises a `NameError`</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="P37" s="5" t="inlineStr">
         <is>
           <t>Python implicitly passes `tax_rate` as a hidden parameter</t>
         </is>
       </c>
-      <c r="Q37" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="Q37" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" ht="184.8000030517578" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>Python - MCQ - 8.2.27</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>A visitor-counting app on a museum's entry gate increments a shared counter each time someone walks in, using a function that modifies a variable defined outside it.
 ```python
@@ -3480,328 +3545,315 @@
 What is printed?</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>The global keyword tells Python that counter inside the function refers to the outer global variable rather than creating a new local one, so each call genuinely increments the same global counter, ending at 2 after two calls.</t>
         </is>
       </c>
-      <c r="D38" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
+      <c r="D38" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G38" s="4" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H38" s="4" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>python</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>functions</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
         <is>
           <t>variable-scope-and-legb</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="L38" s="4" t="n"/>
+      <c r="M38" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="N38" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="O38" s="5" t="inlineStr">
         <is>
           <t>An error, since global cannot be used this way</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="P38" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Q38" t="n">
+      <c r="Q38" s="4" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="39" ht="26.39999961853027" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>Python - MCQ - 8.2.28</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>A quiz app checks every answer in a list against a passing threshold using a flag variable flipped inside a loop, just to confirm every item passes. What single built-in call replaces this entire pattern?</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>`all()` takes a sequence and returns `True` only if every item is truthy, which is exactly the flag-and-loop pattern collapsed into one call, removing the need to manage a flag variable by hand.</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>A requirement says users aged 18 or above are eligible, but `eligible(age)` returns `age &gt; 18`. Which boundary test exposes the bug?</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Age 18 is the exact boundary: the requirement accepts it, while the faulty condition rejects it.</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" s="4" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H39" s="4" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>python</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>functions</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>built-in-functions</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>`any(sequence)`</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>`len(sequence)` == 0</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>`sum(sequence)` &gt; 0</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>`all(sequence)`</t>
-        </is>
-      </c>
-      <c r="Q39" t="n">
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>function-testing</t>
+        </is>
+      </c>
+      <c r="L39" s="4" t="n"/>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>Call `eligible(25)`, which both conditions accept</t>
+        </is>
+      </c>
+      <c r="N39" s="5" t="inlineStr">
+        <is>
+          <t>Call the function without an argument and treat the resulting TypeError as a boundary result</t>
+        </is>
+      </c>
+      <c r="O39" s="5" t="inlineStr">
+        <is>
+          <t>Rename the parameter from `age` to `years` without testing behaviour</t>
+        </is>
+      </c>
+      <c r="P39" s="5" t="inlineStr">
+        <is>
+          <t>Call `eligible(18)` and expect `True`</t>
+        </is>
+      </c>
+      <c r="Q39" s="4" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="40" ht="39.59999847412109" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>Python - MCQ - 8.2.29</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>A museum's visitor counter function tries to increment a shared counter variable but forgets to declare it as global inside the function.
-```python
-counter = 0
-def increment():
-    counter = counter + 1
-increment()
-```
-What happens when `increment()` is called?</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Because the function assigns to counter anywhere in its body, Python treats counter as local to that function for its entire execution; this makes the right-hand side try to read a local counter that has no value yet, raising an `UnboundLocalError`.</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Compare two implementations of `area(width, height)`. A returns the product. B prints the product and returns nothing. A caller must reuse the area in another calculation. Which is better?</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Returning the value lets callers compose further calculations; printing is only a display side effect and yields `None` to the caller.</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>evaluate</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>return-values</t>
+        </is>
+      </c>
+      <c r="L40" s="4" t="n"/>
+      <c r="M40" s="5" t="inlineStr">
+        <is>
+          <t>B, because printed values automatically become return values</t>
+        </is>
+      </c>
+      <c r="N40" s="5" t="inlineStr">
+        <is>
+          <t>B, because a function may not return a numeric result</t>
+        </is>
+      </c>
+      <c r="O40" s="5" t="inlineStr">
+        <is>
+          <t>A, because returning the value lets the caller reuse it</t>
+        </is>
+      </c>
+      <c r="P40" s="5" t="inlineStr">
+        <is>
+          <t>They are interchangeable even when the caller multiplies the result again</t>
+        </is>
+      </c>
+      <c r="Q40" s="4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" ht="26.39999961853027" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Python - MCQ - 8.2.30</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>A function calculates a total correctly but the caller receives `None` because the function only evaluates `price * quantity`. What is the smallest correct repair?</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Adding `return` to the existing expression sends the calculated value back without redesigning the function.</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H41" s="4" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>python</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>functions</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>variable-scope-and-legb</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>It silently does nothing at all and counter simply stays at 0</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>It raises a `NameError` because counter was technically never defined anywhere</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>It raises an error, because assigning to counter makes it local before it has a value</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>The variable counter becomes 1 globally after this call</t>
-        </is>
-      </c>
-      <c r="Q40" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Python - MCQ - 8.2.30</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>A ride-hailing app has a status variable defined at the global, enclosing, and local level all at once, and a developer wants to trace exactly what gets printed at each level.
-```python
-value = "global"
-def outer():
-    value = "enclosing"
-    def inner():
-        value = "local"
-        print(value)
-    inner()
-    print(value)
-outer()
-print(value)
-```
-What is printed, in order?</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Each `print(value)` resolves to the nearest matching scope following Local, Enclosing, Global, Built-in order: inner's own local 'local', then outer's local 'enclosing', then the top-level global 'global'.</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>analyze</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>python - Set 2</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>python</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>functions</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>variable-scope-and-legb</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>local, enclosing, global</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>local, global, enclosing</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>global, enclosing, local</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>global, global, global</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>return-values</t>
+        </is>
+      </c>
+      <c r="L41" s="4" t="n"/>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>Change the expression to `return price * quantity`</t>
+        </is>
+      </c>
+      <c r="N41" s="5" t="inlineStr">
+        <is>
+          <t>Add a global variable and rewrite every caller around shared state</t>
+        </is>
+      </c>
+      <c r="O41" s="5" t="inlineStr">
+        <is>
+          <t>Print the expression twice and assume the second print becomes a return value</t>
+        </is>
+      </c>
+      <c r="P41" s="5" t="inlineStr">
+        <is>
+          <t>Remove both parameters from the function</t>
+        </is>
+      </c>
+      <c r="Q41" s="4" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>